--- a/Lab work/Lab3_Kuntal Das.xlsx
+++ b/Lab work/Lab3_Kuntal Das.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anudip Foundation\Lab work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44DE7F18-1F3F-48E9-B547-416ED7607517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB59FA3-6206-4373-9B51-3013C23D2BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-14009]yyyy/mm/dd;@"/>
   </numFmts>
@@ -188,7 +188,9 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{DFF62D1A-465F-4637-B129-C234659152E3}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
